--- a/Project/outputs/tables/table_adf_tests.xlsx
+++ b/Project/outputs/tables/table_adf_tests.xlsx
@@ -467,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-6.4395</v>
+        <v>-7.0681</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.4317</v>
+        <v>-3.4314</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.8621</v>
+        <v>-2.862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,20 +487,20 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-6.3112</v>
+        <v>-6.4742</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.4317</v>
+        <v>-3.4314</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.8621</v>
+        <v>-2.862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -511,20 +511,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.3738</v>
+        <v>-6.9072</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.4317</v>
+        <v>-3.4314</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8621</v>
+        <v>-2.862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,20 +535,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6.3643</v>
+        <v>-7.036</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.4317</v>
+        <v>-3.4314</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.8621</v>
+        <v>-2.862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-7.2082</v>
+        <v>-7.9756</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.4317</v>
+        <v>-3.4314</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8621</v>
+        <v>-2.862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.7816</v>
+        <v>-6.2228</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4317</v>
+        <v>-3.4314</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8621</v>
+        <v>-2.862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.3328</v>
+        <v>-6.9256</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.432</v>
+        <v>-3.4314</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8623</v>
+        <v>-2.862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,17 +631,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-6.1348</v>
+        <v>-5.0927</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4317</v>
+        <v>-3.4316</v>
       </c>
       <c r="E9" t="n">
         <v>-2.8621</v>
